--- a/光伏配储项目/电价数据/2026/辉鸿站.xlsx
+++ b/光伏配储项目/电价数据/2026/辉鸿站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51479</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75173</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57978</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58684</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52119</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5131599999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43813</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42495</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43708</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42114</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44297</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12077</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09902</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10924</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10087</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11954</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04218</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.08945</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.14155</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.12213</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.09182999999999999</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09054999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05759</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.11665</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.10079</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14548</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21343</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23091</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24322</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2194</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.27521</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.12809</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.27409</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27716</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21227</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.57411</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.44032</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.43716</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.65718</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.55143</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43717</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42713</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5634199999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44835</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.60377</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8034600000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61949</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.64589</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.74173</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9623200000000001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6587000000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58173</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7555700000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.46498</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62434</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6057</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51701</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48067</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46545</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42598</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6936100000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.91018</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.61813</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.44122</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6427</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48829</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51734</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50454</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50522</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48675</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41713</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.47829</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.54104</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.45432</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42743</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43694</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4704700000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.48531</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.75324</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.56216</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.46711</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.7726000000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.7138099999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.61483</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.70885</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.56425</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.8676</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.7789199999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.40383</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.46046</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.74773</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.55657</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.54232</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.54544</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43063</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40864</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.73966</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.53999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49254</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.58247</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5449400000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6736</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.61858</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.72258</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43017</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77177</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.48578</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.40504</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44101</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43024</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3347</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51085</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.44069</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.44034</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44556</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43031</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44611</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47367</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44631</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39603</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21813</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.26886</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27448</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.71888</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.47632</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.55116</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.48054</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.48278</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.47837</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.53577</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.59062</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.61939</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.4755</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.49156</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46689</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.46208</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.54731</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.53149</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.61449</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.59614</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59133</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.47024</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48828</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40514</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.45368</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43838</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46206</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44704</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3421</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45159</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26361</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.11219</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24229</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.21404</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.55675</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.41522</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.21303</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.46776</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.24664</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.49016</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16071</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.42599</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32532</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04471</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.26735</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02984</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04636999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.16434</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.19957</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.18458</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14201</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.0433</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.0377</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04524</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2183</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05722</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04922</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04416</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00098</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.07031</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03696</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09827</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46672</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41531</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35012</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65149</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44118</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.41902</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10254</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04348</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04414</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.6567999999999999</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.05967</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.09644</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.24115</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.008960000000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04576</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04361</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.15257</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.15169</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04739</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.0479</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19977</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14273</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33494</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31685</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28801</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27115</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17091</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14769</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15857</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2361</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28042</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50768</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78103</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92041</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49457</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91428</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86298</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29634</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8876799999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316499999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18727</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8686200000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.52708</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33103</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03304</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53095</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79112</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52704</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77311</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77765</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87679</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87393</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49327</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40006</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20716</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87885</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55103</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62202</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53837</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45585</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42428</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43718</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45269</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43285</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58297</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42495</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59461</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.59882</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.68475</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46924</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.57797</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8516</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.60902</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8750399999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.83125</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.85937</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43855</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6631</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.41351</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40746</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.44896</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35273</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91686</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46234</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47438</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45961</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4956</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16844</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19886</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19229</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28823</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25552</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43806</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44867</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5893999999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8879199999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.55372</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1546</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69835</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7889700000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65932</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5718099999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49989</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4392200000000001</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49655</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43345</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41034</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43357</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42495</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44686</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43098</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41244</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49326</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55928</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.25405</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.19786</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.10226</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26113</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25516</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28552</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.56802</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.45929</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8223200000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46136</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43398</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32191</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23078</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14635</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14832</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15516</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.13694</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13454</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.1419</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13885</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2529</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13972</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25658</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25074</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13723</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.11559</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11071</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10962</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.13696</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13939</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14488</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44543</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44624</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43555</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43498</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.43984</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34692</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53237</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26736</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20701</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25017</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24427</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26327</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2419</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28554</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25773</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35877</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41351</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43094</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.6234</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.69955</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.73026</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24725</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.6746799999999999</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.57608</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43483</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69065</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5120399999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22505</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.33969</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.45014</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.87381</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.8671599999999999</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.86177</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.54774</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.46745</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.46139</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.45326</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.45827</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.45445</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.46394</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.5625800000000001</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>1.12023</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.21836</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.349</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.7813300000000001</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41088</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65622</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7626799999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45523</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34352</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26517</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14862</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.27582</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.27705</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20146</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24815</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21819</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25783</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28558</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42693</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.57357</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5329700000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.53655</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.41273</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7221000000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48069</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.73898</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.92791</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.82673</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.17681</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.7880900000000001</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.90654</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42791</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35904</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52458</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47734</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47819</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40604</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44438</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44367</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.54941</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.4923</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44471</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.49745</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44313</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45631</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41688</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.45271</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.44634</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.52213</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38253</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28141</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64491</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.48006</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40969</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43466</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48926</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43592</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.43493</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.4589</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.47516</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.62125</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6416900000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.78987</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7992999999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5786399999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52312</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8250299999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7712100000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62354</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6725599999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44206</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47074</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47364</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46671</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41522</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.54823</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42589</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43918</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43389</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44292</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41551</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45107</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20634</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.01843</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.43806</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10842</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.17739</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.28847</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41452</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43229</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36251</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22252</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23115</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25029</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24834</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13584</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.23944</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04235</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17153</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23449</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25733</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26058</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.22743</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27383</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34678</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19568</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25777</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01734</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00054</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00647</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1401</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.01307</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03946</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03888</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04159</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03917</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04831000000000001</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02448</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03878</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04951</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00049</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04517</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02105</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03748</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19193</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.25051</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.27757</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.21154</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.28347</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.66185</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.42417</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.46037</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.72556</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8544700000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.81472</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.69669</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03131</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2328</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.25462</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.23584</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.24702</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.23675</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.00226</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.21429</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.01792</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.23568</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00957</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.03732</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.23225</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.24331</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.23721</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.22303</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25571</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27433</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3213</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.17903</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.51602</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.50913</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.52438</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.40195</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.41451</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14143</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27609</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27023</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33059</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.5065500000000001</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4695299999999999</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47531</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.49226</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40628</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4753500000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.62294</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41875</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3654</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4729</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44188</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5764600000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5915199999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.49444</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.60553</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.65884</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.54112</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.57321</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4927</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6534099999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.79692</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.74466</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5431</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.50796</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36945</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.15759</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.25995</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.27473</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06711</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.18224</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20496</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15207</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.02167</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26313</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15416</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05226</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.07575</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08514000000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.24684</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08896</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05737</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.19789</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15976</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17853</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.4672</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.44027</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42903</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36375</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9418099999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.53606</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.47692</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.42844</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.66274</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01869</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.6500499999999999</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.69413</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.51281</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.6088899999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.5029100000000001</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42483</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36183</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.16106</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13498</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.18068</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.15135</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04162</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.22134</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.5092</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.20952</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.49665</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.20293</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.23505</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.13897</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.13771</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5942200000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.27527</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.17808</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.23062</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47419</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38257</v>
       </c>
     </row>
   </sheetData>
